--- a/港岛-山顶区-Mount Nicholson I/Mount Nicholson I_销控明细表.xlsx
+++ b/港岛-山顶区-Mount Nicholson I/Mount Nicholson I_销控明细表.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2017-01-22</t>
+          <t>2017-01-23</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -802,7 +802,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2018-04-15</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -868,7 +868,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2017-11-23</t>
+          <t>2017-11-24</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2016-05-05</t>
+          <t>2016-05-06</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2016-03-15</t>
+          <t>2016-03-16</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2017-03-12</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2016-12-12</t>
+          <t>2016-12-13</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2017-06-05</t>
+          <t>2017-06-06</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2016-12-13</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2019-06-24</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2018-04-27</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2017-08-16</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2017-09-19</t>
+          <t>2017-09-20</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1976,7 +1976,7 @@
         <is>
           <t>1号屋
 9950呎 (4+房)
-(17年-01月-22日)
+(17年-01月-23日)
 $10.80亿
 $108,543/呎</t>
         </is>
@@ -1985,7 +1985,7 @@
         <is>
           <t>2号屋
 9217呎 (4+房)
-(18年-04月-15日)
+(18年-04月-16日)
 $13.99亿
 $151,785/呎</t>
         </is>
@@ -1994,7 +1994,7 @@
         <is>
           <t>3号屋
 9178呎 (4+房)
-(17年-11月-23日)
+(17年-11月-24日)
 $11.64亿
 $126,813/呎</t>
         </is>
@@ -2003,7 +2003,7 @@
         <is>
           <t>5号屋
 9173呎 (4+房)
-(16年-05月-05日)
+(16年-05月-06日)
 $7.40亿
 $80,672/呎</t>
         </is>
@@ -2012,7 +2012,7 @@
         <is>
           <t>6号屋
 9455呎 (4+房)
-(16年-03月-15日)
+(16年-03月-16日)
 $8.30亿
 $87,784/呎</t>
         </is>
@@ -2021,7 +2021,7 @@
         <is>
           <t>7号屋
 8087呎 (4+房)
-(17年-03月-12日)
+(17年-03月-13日)
 $7.20亿
 $89,032/呎</t>
         </is>
@@ -2037,7 +2037,7 @@
         <is>
           <t>8号屋
 8054呎 (4+房)
-(16年-08月-15日)
+(16年-08月-16日)
 $6.30亿
 $78,222/呎</t>
         </is>
@@ -2046,7 +2046,7 @@
         <is>
           <t>9号屋
 8083呎 (4+房)
-(16年-12月-12日)
+(16年-12月-13日)
 $6.00亿
 $74,230/呎</t>
         </is>
@@ -2055,7 +2055,7 @@
         <is>
           <t>10号屋
 8017呎 (4+房)
-(17年-06月-05日)
+(17年-06月-06日)
 $6.64亿
 $82,809/呎</t>
         </is>
@@ -2064,7 +2064,7 @@
         <is>
           <t>11号屋
 7065呎 (3房)
-(16年-12月-13日)
+(16年-12月-14日)
 $5.25亿
 $74,310/呎</t>
         </is>
@@ -2073,7 +2073,7 @@
         <is>
           <t>12号屋
 7042呎 (4+房)
-(23年-05月-15日)
+(23年-05月-16日)
 $5.77亿
 $82,000/呎</t>
         </is>
@@ -2082,7 +2082,7 @@
         <is>
           <t>15号屋
 8674呎 (4+房)
-(19年-06月-24日)
+(19年-06月-25日)
 $9.16亿
 $105,603/呎</t>
         </is>
@@ -2098,7 +2098,7 @@
         <is>
           <t>16号屋
 7978呎 (4+房)
-(19年-06月-02日)
+(19年-06月-03日)
 $7.20亿
 $90,248/呎</t>
         </is>
@@ -2107,7 +2107,7 @@
         <is>
           <t>17号屋
 7984呎 (3房)
-(18年-04月-26日)
+(18年-04月-27日)
 $7.80亿
 $97,695/呎</t>
         </is>
@@ -2116,7 +2116,7 @@
         <is>
           <t>18号屋
 8050呎 (4+房)
-(17年-08月-16日)
+(17年-08月-17日)
 $6.45亿
 $80,124/呎</t>
         </is>
@@ -2125,7 +2125,7 @@
         <is>
           <t>19号屋
 7981呎 (4+房)
-(17年-09月-19日)
+(17年-09月-20日)
 $6.20亿
 $77,685/呎</t>
         </is>
